--- a/data/nzd0068/nzd0068.xlsx
+++ b/data/nzd0068/nzd0068.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7187,6 +7187,60 @@
       <c r="G251" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>312.02</v>
+      </c>
+      <c r="C252" t="n">
+        <v>322.23</v>
+      </c>
+      <c r="D252" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="E252" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="F252" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>312.02</v>
+      </c>
+      <c r="C253" t="n">
+        <v>317.33</v>
+      </c>
+      <c r="D253" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="E253" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="F253" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10114,6 +10168,26 @@
       </c>
       <c r="B291" t="n">
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -10282,28 +10356,28 @@
         <v>0.0327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1984822752026041</v>
+        <v>0.2186457184052489</v>
       </c>
       <c r="J2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01054340375258578</v>
+        <v>0.01294369545126983</v>
       </c>
       <c r="M2" t="n">
-        <v>11.94817893715896</v>
+        <v>11.9452209928421</v>
       </c>
       <c r="N2" t="n">
-        <v>223.9289242936348</v>
+        <v>223.3775449371064</v>
       </c>
       <c r="O2" t="n">
-        <v>14.96425488601537</v>
+        <v>14.94582031663389</v>
       </c>
       <c r="P2" t="n">
-        <v>294.0370562299723</v>
+        <v>293.8411960466179</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10360,28 +10434,28 @@
         <v>0.0355</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5496858631254258</v>
+        <v>0.5794600995504771</v>
       </c>
       <c r="J3" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K3" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06711134915760986</v>
+        <v>0.0745988748841071</v>
       </c>
       <c r="M3" t="n">
-        <v>13.46453648743377</v>
+        <v>13.48810893935192</v>
       </c>
       <c r="N3" t="n">
-        <v>257.5958867972006</v>
+        <v>258.4032117201534</v>
       </c>
       <c r="O3" t="n">
-        <v>16.04979397989895</v>
+        <v>16.07492493668799</v>
       </c>
       <c r="P3" t="n">
-        <v>285.9465016489244</v>
+        <v>285.6609277646895</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10438,28 +10512,28 @@
         <v>0.0286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07009147493677573</v>
+        <v>-0.03925990043174917</v>
       </c>
       <c r="J4" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K4" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00226016516249683</v>
+        <v>0.0007083078725244052</v>
       </c>
       <c r="M4" t="n">
-        <v>9.343988438036776</v>
+        <v>9.400154447496481</v>
       </c>
       <c r="N4" t="n">
-        <v>130.0373746343614</v>
+        <v>131.8975688843862</v>
       </c>
       <c r="O4" t="n">
-        <v>11.4033931193466</v>
+        <v>11.48466668582011</v>
       </c>
       <c r="P4" t="n">
-        <v>299.5292070912732</v>
+        <v>299.2268467440062</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10516,28 +10590,28 @@
         <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2472780912889826</v>
+        <v>-0.2040315390508303</v>
       </c>
       <c r="J5" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K5" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02031104937073347</v>
+        <v>0.01374540222114962</v>
       </c>
       <c r="M5" t="n">
-        <v>10.75997497362295</v>
+        <v>10.88667151674837</v>
       </c>
       <c r="N5" t="n">
-        <v>177.4373231790886</v>
+        <v>181.7753442350775</v>
       </c>
       <c r="O5" t="n">
-        <v>13.3205601676164</v>
+        <v>13.48240869559581</v>
       </c>
       <c r="P5" t="n">
-        <v>307.5531576768252</v>
+        <v>307.130343505813</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -10594,28 +10668,28 @@
         <v>0.036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2381766056808952</v>
+        <v>-0.2046933045952996</v>
       </c>
       <c r="J6" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K6" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01940098453979389</v>
+        <v>0.01439751597707939</v>
       </c>
       <c r="M6" t="n">
-        <v>10.01327327149144</v>
+        <v>10.10300318052339</v>
       </c>
       <c r="N6" t="n">
-        <v>171.9883967101623</v>
+        <v>174.045083277535</v>
       </c>
       <c r="O6" t="n">
-        <v>13.1144346698652</v>
+        <v>13.19261472481991</v>
       </c>
       <c r="P6" t="n">
-        <v>305.0061730936625</v>
+        <v>304.6781965603096</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -10653,7 +10727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19887,6 +19961,80 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>-35.333499225852776,173.18627214226998</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>-35.332971779453715,173.18563882345134</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>-35.33235943034504,173.18514153879624</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-35.331837164863366,173.18449990485684</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-35.33120759859193,173.18403019415098</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-35.333499225852776,173.18627214226998</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>-35.3329450097004,173.1856817170574</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-35.33235943034504,173.18514153879624</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-35.331837164863366,173.18449990485684</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-35.33120759859193,173.18403019415098</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0068/nzd0068.xlsx
+++ b/data/nzd0068/nzd0068.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:G254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7224,23 +7224,50 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>312.02</v>
+        <v>304.27</v>
       </c>
       <c r="C253" t="n">
         <v>317.33</v>
       </c>
       <c r="D253" t="n">
-        <v>316.9</v>
+        <v>310.47</v>
       </c>
       <c r="E253" t="n">
-        <v>328.06</v>
+        <v>320.93</v>
       </c>
       <c r="F253" t="n">
-        <v>319.58</v>
+        <v>312.74</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>300.89</v>
+      </c>
+      <c r="C254" t="n">
+        <v>314.02</v>
+      </c>
+      <c r="D254" t="n">
+        <v>307.23</v>
+      </c>
+      <c r="E254" t="n">
+        <v>317.82</v>
+      </c>
+      <c r="F254" t="n">
+        <v>311.16</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10188,6 +10215,16 @@
       </c>
       <c r="B293" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -10356,28 +10393,28 @@
         <v>0.0327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2186457184052489</v>
+        <v>0.2134601707105487</v>
       </c>
       <c r="J2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01294369545126983</v>
+        <v>0.01249300621896188</v>
       </c>
       <c r="M2" t="n">
-        <v>11.9452209928421</v>
+        <v>11.87294956415882</v>
       </c>
       <c r="N2" t="n">
-        <v>223.3775449371064</v>
+        <v>221.9591697211843</v>
       </c>
       <c r="O2" t="n">
-        <v>14.94582031663389</v>
+        <v>14.8982941883017</v>
       </c>
       <c r="P2" t="n">
-        <v>293.8411960466179</v>
+        <v>293.8915451857184</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10434,28 +10471,28 @@
         <v>0.0355</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5794600995504771</v>
+        <v>0.5893567346394506</v>
       </c>
       <c r="J3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0745988748841071</v>
+        <v>0.07748423304497498</v>
       </c>
       <c r="M3" t="n">
-        <v>13.48810893935192</v>
+        <v>13.47828430822647</v>
       </c>
       <c r="N3" t="n">
-        <v>258.4032117201534</v>
+        <v>258.012171786959</v>
       </c>
       <c r="O3" t="n">
-        <v>16.07492493668799</v>
+        <v>16.06275729091861</v>
       </c>
       <c r="P3" t="n">
-        <v>285.6609277646895</v>
+        <v>285.5655094292881</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10512,28 +10549,28 @@
         <v>0.0286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03925990043174917</v>
+        <v>-0.03711715748359405</v>
       </c>
       <c r="J4" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K4" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007083078725244052</v>
+        <v>0.0006416507514060976</v>
       </c>
       <c r="M4" t="n">
-        <v>9.400154447496481</v>
+        <v>9.371384265102209</v>
       </c>
       <c r="N4" t="n">
-        <v>131.8975688843862</v>
+        <v>130.8956704913266</v>
       </c>
       <c r="O4" t="n">
-        <v>11.48466668582011</v>
+        <v>11.4409645787113</v>
       </c>
       <c r="P4" t="n">
-        <v>299.2268467440062</v>
+        <v>299.2054928275367</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10590,28 +10627,28 @@
         <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2040315390508303</v>
+        <v>-0.1967915082830188</v>
       </c>
       <c r="J5" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01374540222114962</v>
+        <v>0.01294107623129492</v>
       </c>
       <c r="M5" t="n">
-        <v>10.88667151674837</v>
+        <v>10.87841615484487</v>
       </c>
       <c r="N5" t="n">
-        <v>181.7753442350775</v>
+        <v>180.7887011882741</v>
       </c>
       <c r="O5" t="n">
-        <v>13.48240869559581</v>
+        <v>13.44576889539137</v>
       </c>
       <c r="P5" t="n">
-        <v>307.130343505813</v>
+        <v>307.0589402331029</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -10668,28 +10705,28 @@
         <v>0.036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2046933045952996</v>
+        <v>-0.200536208404839</v>
       </c>
       <c r="J6" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K6" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01439751597707939</v>
+        <v>0.01398816119465818</v>
       </c>
       <c r="M6" t="n">
-        <v>10.10300318052339</v>
+        <v>10.08318582075131</v>
       </c>
       <c r="N6" t="n">
-        <v>174.045083277535</v>
+        <v>172.9945375676763</v>
       </c>
       <c r="O6" t="n">
-        <v>13.19261472481991</v>
+        <v>13.15273878580717</v>
       </c>
       <c r="P6" t="n">
-        <v>304.6781965603096</v>
+        <v>304.6370229276517</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -10727,7 +10764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:G254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20006,7 +20043,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>-35.333499225852776,173.18627214226998</t>
+          <t>-35.333456885684775,173.18633998439196</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -20016,22 +20053,59 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>-35.33235943034504,173.18514153879624</t>
+          <t>-35.33232430200952,173.18519782541654</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>-35.331837164863366,173.18449990485684</t>
+          <t>-35.33179821252036,173.18456231891753</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-35.33120759859193,173.18403019415098</t>
+          <t>-35.33117023070148,173.18409006929903</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-35.333438419896325,173.1863695722888</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>-35.33292692645024,173.18571069210998</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>-35.332306601251965,173.185226187552</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-35.331781222077325,173.18458954298413</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-35.33116159893309,173.18410390010024</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0068/nzd0068.xlsx
+++ b/data/nzd0068/nzd0068.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:G255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7266,6 +7266,33 @@
         <v>311.16</v>
       </c>
       <c r="G254" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>300.89</v>
+      </c>
+      <c r="C255" t="n">
+        <v>310.77</v>
+      </c>
+      <c r="D255" t="n">
+        <v>305.08</v>
+      </c>
+      <c r="E255" t="n">
+        <v>314.22</v>
+      </c>
+      <c r="F255" t="n">
+        <v>306.79</v>
+      </c>
+      <c r="G255" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -7282,7 +7309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10225,6 +10252,16 @@
       </c>
       <c r="B294" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -10393,28 +10430,28 @@
         <v>0.0327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2134601707105487</v>
+        <v>0.2144249233592799</v>
       </c>
       <c r="J2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01249300621896188</v>
+        <v>0.01272522040080126</v>
       </c>
       <c r="M2" t="n">
-        <v>11.87294956415882</v>
+        <v>11.82980922833817</v>
       </c>
       <c r="N2" t="n">
-        <v>221.9591697211843</v>
+        <v>221.0772755533332</v>
       </c>
       <c r="O2" t="n">
-        <v>14.8982941883017</v>
+        <v>14.86866757827793</v>
       </c>
       <c r="P2" t="n">
-        <v>293.8915451857184</v>
+        <v>293.8821084103978</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10471,28 +10508,28 @@
         <v>0.0355</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5893567346394506</v>
+        <v>0.5964961247128572</v>
       </c>
       <c r="J3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07748423304497498</v>
+        <v>0.07982731879181915</v>
       </c>
       <c r="M3" t="n">
-        <v>13.47828430822647</v>
+        <v>13.45634708393997</v>
       </c>
       <c r="N3" t="n">
-        <v>258.012171786959</v>
+        <v>257.3297036587753</v>
       </c>
       <c r="O3" t="n">
-        <v>16.06275729091861</v>
+        <v>16.04149942052723</v>
       </c>
       <c r="P3" t="n">
-        <v>285.5655094292881</v>
+        <v>285.4965462578114</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10549,28 +10586,28 @@
         <v>0.0286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03711715748359405</v>
+        <v>-0.03168754430451075</v>
       </c>
       <c r="J4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006416507514060976</v>
+        <v>0.000471593350087729</v>
       </c>
       <c r="M4" t="n">
-        <v>9.371384265102209</v>
+        <v>9.35701989699969</v>
       </c>
       <c r="N4" t="n">
-        <v>130.8956704913266</v>
+        <v>130.5587101198531</v>
       </c>
       <c r="O4" t="n">
-        <v>11.4409645787113</v>
+        <v>11.42622904198289</v>
       </c>
       <c r="P4" t="n">
-        <v>299.2054928275367</v>
+        <v>299.1518760590889</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10627,28 +10664,28 @@
         <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1967915082830188</v>
+        <v>-0.1869840439252253</v>
       </c>
       <c r="J5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01294107623129492</v>
+        <v>0.01177008394481704</v>
       </c>
       <c r="M5" t="n">
-        <v>10.87841615484487</v>
+        <v>10.88285390351578</v>
       </c>
       <c r="N5" t="n">
-        <v>180.7887011882741</v>
+        <v>180.6814724043398</v>
       </c>
       <c r="O5" t="n">
-        <v>13.44576889539137</v>
+        <v>13.4417808494388</v>
       </c>
       <c r="P5" t="n">
-        <v>307.0589402331029</v>
+        <v>306.9623873638816</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -10705,28 +10742,28 @@
         <v>0.036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.200536208404839</v>
+        <v>-0.194574679194955</v>
       </c>
       <c r="J6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01398816119465818</v>
+        <v>0.01328830693387406</v>
       </c>
       <c r="M6" t="n">
-        <v>10.08318582075131</v>
+        <v>10.07267149021252</v>
       </c>
       <c r="N6" t="n">
-        <v>172.9945375676763</v>
+        <v>172.5307557502918</v>
       </c>
       <c r="O6" t="n">
-        <v>13.15273878580717</v>
+        <v>13.13509633578269</v>
       </c>
       <c r="P6" t="n">
-        <v>304.6370229276517</v>
+        <v>304.5782237392031</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -10764,7 +10801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:G255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20109,6 +20146,43 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-35.333438419896325,173.1863695722888</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>-35.33290917098635,173.18573914192245</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>-35.33229485537521,173.185245008098</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-35.331761554675786,173.18462105635888</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-35.33113772498313,173.18414215363</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
